--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(1).xlsx
@@ -1149,7 +1149,25 @@
     <t>毕竟，当一个人连身份、记忆这些本应最理所应当的东西都握不住的时候，他又能再失去些什么呢？</t>
   </si>
   <si>
-    <t>loadScript(终局（中）_4, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 4)</t>
+    </r>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=111; gotomainline=终局（中）_4</t>
@@ -1722,7 +1740,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1884,6 +1902,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2337,12 +2360,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -7165,7 +7191,7 @@
       <c r="J113" t="s">
         <v>15</v>
       </c>
-      <c r="K113" t="s">
+      <c r="K113" s="2" t="s">
         <v>367</v>
       </c>
       <c r="L113" t="s">
